--- a/source_data/workbooks/Source_Data_ED_Fig6.xlsx
+++ b/source_data/workbooks/Source_Data_ED_Fig6.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="83">
   <si>
     <t>plot_order</t>
   </si>
@@ -176,12 +176,72 @@
     <t>recomputed_sd_subsample</t>
   </si>
   <si>
+    <t>system_description</t>
+  </si>
+  <si>
     <t>Extended Data 6c</t>
   </si>
   <si>
     <t>SEA-AD held-out</t>
   </si>
   <si>
+    <t>UNI ABMIL</t>
+  </si>
+  <si>
+    <t>TITAN Linear Probe</t>
+  </si>
+  <si>
+    <t>MUSK ABMIL</t>
+  </si>
+  <si>
+    <t>TITAN Fine-tune</t>
+  </si>
+  <si>
+    <t>CA1 %GFAP area (GFAP IHC)</t>
+  </si>
+  <si>
+    <t>Reactive fraction</t>
+  </si>
+  <si>
+    <t>Reactive/astrogl. ratio 35µm</t>
+  </si>
+  <si>
+    <t>Peripyramidal react. 35µm</t>
+  </si>
+  <si>
+    <t>partial_pearson_r</t>
+  </si>
+  <si>
+    <t>SD across 100 repeated 80% donor subsamples</t>
+  </si>
+  <si>
+    <t>SD across 100 repeated 80% donor subsamples; plotted value/SD rounded to 3 decimals</t>
+  </si>
+  <si>
+    <t>trained WSI predictor</t>
+  </si>
+  <si>
+    <t>fixed tissue measurement</t>
+  </si>
+  <si>
+    <t>uni_gated_abmil</t>
+  </si>
+  <si>
+    <t>titan_linear_probe</t>
+  </si>
+  <si>
+    <t>musk_gated_abmil</t>
+  </si>
+  <si>
+    <t>titan_finetune</t>
+  </si>
+  <si>
+    <t>SEA-AD HALO serial GFAP immunostain</t>
+  </si>
+  <si>
+    <t>NuClass April-compatible reconstruction</t>
+  </si>
+  <si>
     <t>UNI-ABMIL</t>
   </si>
   <si>
@@ -204,39 +264,6 @@
   </si>
   <si>
     <t>Peripyramidal astrocyte-lineage reactivity, 35 um</t>
-  </si>
-  <si>
-    <t>partial_pearson_r</t>
-  </si>
-  <si>
-    <t>SD across 100 repeated 80% donor subsamples</t>
-  </si>
-  <si>
-    <t>SD across 100 repeated 80% donor subsamples; plotted value/SD rounded to 3 decimals</t>
-  </si>
-  <si>
-    <t>trained WSI predictor</t>
-  </si>
-  <si>
-    <t>fixed tissue measurement</t>
-  </si>
-  <si>
-    <t>uni_gated_abmil</t>
-  </si>
-  <si>
-    <t>titan_linear_probe</t>
-  </si>
-  <si>
-    <t>musk_gated_abmil</t>
-  </si>
-  <si>
-    <t>titan_finetune</t>
-  </si>
-  <si>
-    <t>SEA-AD HALO serial GFAP immunostain</t>
-  </si>
-  <si>
-    <t>NuClass April-compatible reconstruction</t>
   </si>
 </sst>
 </file>
@@ -2101,14 +2128,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="39.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
-    <col min="5" max="5" width="55.7109375" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
@@ -2128,9 +2155,10 @@
     <col min="27" max="27" width="41.7109375" customWidth="1"/>
     <col min="28" max="28" width="20.7109375" customWidth="1"/>
     <col min="29" max="29" width="25.7109375" customWidth="1"/>
+    <col min="30" max="30" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:30">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2218,25 +2246,28 @@
       <c r="AC1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
         <v>38</v>
@@ -2278,33 +2309,36 @@
         <v>1</v>
       </c>
       <c r="Y2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AA2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29">
+        <v>69</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
         <v>38</v>
@@ -2346,33 +2380,36 @@
         <v>1</v>
       </c>
       <c r="Y3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AA3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
+        <v>70</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
         <v>38</v>
@@ -2414,33 +2451,36 @@
         <v>1</v>
       </c>
       <c r="Y4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AA4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29">
+        <v>71</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
         <v>38</v>
@@ -2482,33 +2522,36 @@
         <v>1</v>
       </c>
       <c r="Y5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AA5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29">
+        <v>72</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
         <v>38</v>
@@ -2550,13 +2593,13 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AA6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AB6">
         <v>0.4144588328616661</v>
@@ -2564,25 +2607,28 @@
       <c r="AC6">
         <v>0.0825103513655209</v>
       </c>
-    </row>
-    <row r="7" spans="1:29">
+      <c r="AD6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
         <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
         <v>38</v>
@@ -2624,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AA7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB7">
         <v>0.4898484638752191</v>
@@ -2638,25 +2684,28 @@
       <c r="AC7">
         <v>0.1014424853810143</v>
       </c>
-    </row>
-    <row r="8" spans="1:29">
+      <c r="AD7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" t="s">
         <v>38</v>
@@ -2698,13 +2747,13 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AA8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB8">
         <v>0.5325292396140471</v>
@@ -2712,25 +2761,28 @@
       <c r="AC8">
         <v>0.08226816707665779</v>
       </c>
-    </row>
-    <row r="9" spans="1:29">
+      <c r="AD8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
         <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" t="s">
         <v>38</v>
@@ -2772,19 +2824,22 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AA9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB9">
         <v>0.5052486204359486</v>
       </c>
       <c r="AC9">
         <v>0.0917906417567271</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
